--- a/outputs/schedule_kenkere.xlsx
+++ b/outputs/schedule_kenkere.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -706,11 +706,11 @@
 []</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Chaitanya Nahar
-61% pred | 0% hist
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
+40% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -724,9 +724,9 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Cardio Barre
+          <t>Barre 57
 Raunak Khemuka
-20% pred | 0% hist
+85% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -853,14 +853,7 @@
 []</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G11" s="6" t="n"/>
       <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
@@ -890,14 +883,7 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B13" s="6" t="n"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Mat 57
@@ -927,9 +913,9 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>FIT
+          <t>Cardio Barre
 Chaitanya Nahar
-46% pred | 0% hist
+40% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1037,14 +1023,7 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B18" s="6" t="n"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Mat 57
@@ -1072,7 +1051,14 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="9" t="inlineStr">
@@ -1083,7 +1069,14 @@
 []</t>
         </is>
       </c>
-      <c r="F19" s="6" t="n"/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
     </row>
@@ -1093,14 +1086,7 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-50% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B20" s="6" t="n"/>
       <c r="C20" s="7" t="inlineStr">
         <is>
           <t>FIT
@@ -1149,6 +1135,27 @@
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1164,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1349,11 +1356,11 @@
 []</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Chaitanya Nahar
-61% pred | 0% hist
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
+40% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1367,9 +1374,9 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Cardio Barre
+          <t>Barre 57
 Raunak Khemuka
-20% pred | 0% hist
+85% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1496,14 +1503,7 @@
 []</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G11" s="6" t="n"/>
       <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
@@ -1533,14 +1533,7 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B13" s="6" t="n"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Mat 57
@@ -1570,9 +1563,9 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>FIT
+          <t>Cardio Barre
 Chaitanya Nahar
-46% pred | 0% hist
+40% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1680,14 +1673,7 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B18" s="6" t="n"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Mat 57
@@ -1715,7 +1701,14 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="9" t="inlineStr">
@@ -1726,7 +1719,14 @@
 []</t>
         </is>
       </c>
-      <c r="F19" s="6" t="n"/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
     </row>
@@ -1736,14 +1736,7 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-50% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B20" s="6" t="n"/>
       <c r="C20" s="7" t="inlineStr">
         <is>
           <t>FIT
@@ -1792,6 +1785,27 @@
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1807,7 +1821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1992,11 +2006,11 @@
 []</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Chaitanya Nahar
-61% pred | 0% hist
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
+40% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2010,9 +2024,9 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Cardio Barre
+          <t>Barre 57
 Raunak Khemuka
-20% pred | 0% hist
+85% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2139,14 +2153,7 @@
 []</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G11" s="6" t="n"/>
       <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
@@ -2176,14 +2183,7 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B13" s="6" t="n"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Mat 57
@@ -2213,9 +2213,9 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>FIT
+          <t>Cardio Barre
 Chaitanya Nahar
-46% pred | 0% hist
+40% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2323,14 +2323,7 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B18" s="6" t="n"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Mat 57
@@ -2358,7 +2351,14 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="9" t="inlineStr">
@@ -2369,7 +2369,14 @@
 []</t>
         </is>
       </c>
-      <c r="F19" s="6" t="n"/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
     </row>
@@ -2379,14 +2386,7 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-50% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B20" s="6" t="n"/>
       <c r="C20" s="7" t="inlineStr">
         <is>
           <t>FIT
@@ -2435,6 +2435,27 @@
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kenkere.xlsx
+++ b/outputs/schedule_kenkere.xlsx
@@ -47,13 +47,13 @@
       <sz val="9"/>
     </font>
     <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="0092400E"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="000C4A6E"/>
-      <sz val="9"/>
     </font>
     <font>
       <color rgb="00065F46"/>
@@ -89,12 +89,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFBEB"/>
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
+        <fgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
     <fill>
@@ -148,10 +148,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -598,16 +598,16 @@
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pushyank Nahar
+31% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="n"/>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
     </row>
@@ -617,8 +617,22 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+52% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -627,90 +641,97 @@
 []</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
 46% pred | 0% hist
 []</t>
         </is>
       </c>
+      <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>08:30</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>08:15</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
 Kajol Kanchan
 46% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+9% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+75% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-54% pred | 0% hist
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+62% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -719,107 +740,149 @@
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pushyank Nahar
+12% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="5" t="n"/>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-57% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-84% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n"/>
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
+84% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Shruti Kulkarni
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="n"/>
+          <t>Cardio Barre
+Chaitanya Nahar
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Kajol Kanchan
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Siddhartha Kusuma
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Chaitanya Nahar
@@ -828,73 +891,45 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n"/>
-    </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
           <t>FIT
-Shruti Kulkarni
+Pushyank Nahar
 20% pred | 0% hist
 []</t>
         </is>
@@ -902,117 +937,208 @@
       <c r="D14" s="6" t="inlineStr">
         <is>
           <t>FIT
-Kajol Kanchan
+Pushyank Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
 Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+100% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
 Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-8% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+0% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
 Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Shruti Kulkarni
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+77% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
@@ -1020,37 +1146,114 @@
 []</t>
         </is>
       </c>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
+77% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>Recovery
-Pushyank Nahar
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+Shruti Kulkarni
+72% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+74% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
 Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1066,7 +1269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1143,16 +1346,16 @@
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pushyank Nahar
+31% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="n"/>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
     </row>
@@ -1162,8 +1365,22 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+52% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -1172,90 +1389,97 @@
 []</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
 46% pred | 0% hist
 []</t>
         </is>
       </c>
+      <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>08:30</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>08:15</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
 Kajol Kanchan
 46% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+9% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+75% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-54% pred | 0% hist
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+62% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1264,107 +1488,149 @@
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pushyank Nahar
+12% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="5" t="n"/>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-57% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-84% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n"/>
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
+84% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Shruti Kulkarni
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="n"/>
+          <t>Cardio Barre
+Chaitanya Nahar
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Kajol Kanchan
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Siddhartha Kusuma
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Chaitanya Nahar
@@ -1373,73 +1639,45 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n"/>
-    </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
           <t>FIT
-Shruti Kulkarni
+Pushyank Nahar
 20% pred | 0% hist
 []</t>
         </is>
@@ -1447,117 +1685,208 @@
       <c r="D14" s="6" t="inlineStr">
         <is>
           <t>FIT
-Kajol Kanchan
+Pushyank Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
 Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+100% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
 Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-8% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+0% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
 Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Shruti Kulkarni
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+77% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
@@ -1565,37 +1894,114 @@
 []</t>
         </is>
       </c>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
+77% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>Recovery
-Pushyank Nahar
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+Shruti Kulkarni
+72% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+74% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
 Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1611,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1688,16 +2094,16 @@
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pushyank Nahar
+31% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="n"/>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
     </row>
@@ -1707,8 +2113,22 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+52% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -1717,90 +2137,97 @@
 []</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
 46% pred | 0% hist
 []</t>
         </is>
       </c>
+      <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>08:30</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>08:15</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
 Kajol Kanchan
 46% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+9% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+75% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-54% pred | 0% hist
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+62% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1809,107 +2236,149 @@
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pushyank Nahar
+12% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="5" t="n"/>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-57% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-84% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n"/>
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
+84% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Shruti Kulkarni
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="n"/>
+          <t>Cardio Barre
+Chaitanya Nahar
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Kajol Kanchan
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Siddhartha Kusuma
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Chaitanya Nahar
@@ -1918,73 +2387,45 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n"/>
-    </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
           <t>FIT
-Shruti Kulkarni
+Pushyank Nahar
 20% pred | 0% hist
 []</t>
         </is>
@@ -1992,117 +2433,208 @@
       <c r="D14" s="6" t="inlineStr">
         <is>
           <t>FIT
-Kajol Kanchan
+Pushyank Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
 Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+100% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
 Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-8% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+0% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+50% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
 Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Shruti Kulkarni
+42% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+77% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
@@ -2110,37 +2642,114 @@
 []</t>
         </is>
       </c>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
+77% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>Recovery
-Pushyank Nahar
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+Shruti Kulkarni
+72% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+74% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
 Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kenkere.xlsx
+++ b/outputs/schedule_kenkere.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -615,8 +615,8 @@
       <c r="D3" s="6" t="inlineStr">
         <is>
           <t>FIT
-Pushyank Nahar
-67% pred | 0% hist
+Kajol Kanchan
+69% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -631,7 +631,7 @@
       <c r="F3" s="6" t="inlineStr">
         <is>
           <t>FIT
-Siddhartha Kusuma
+Shruti Kulkarni
 46% pred | 0% hist
 []</t>
         </is>
@@ -640,59 +640,108 @@
       <c r="H3" s="7" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>08:30</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>07:45</t>
         </is>
       </c>
       <c r="B4" s="7" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-20% pred | 0% hist
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+32% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D4" s="7" t="n"/>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
-22% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>09:00</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>08:15</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
           <t>FIT
-Shruti Kulkarni
-71% pred | 0% hist
+Kajol Kanchan
+37% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F5" s="7" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+92% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
@@ -700,80 +749,87 @@
 []</t>
         </is>
       </c>
-      <c r="H5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="H7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
 85% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-69% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+62% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Siddhartha Kusuma
-23% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+57% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Siddhartha Kusuma
@@ -781,142 +837,121 @@
 []</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-84% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-0% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>Barre 57
+Kajol Kanchan
+69% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Shruti Kulkarni
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="n"/>
+          <t>Back Body Blaze
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-20% pred | 0% hist
+          <t>Barre 57
+Pushyank Nahar
+22% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H12" s="7" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C13" s="7" t="n"/>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Siddhartha Kusuma
+          <t>Barre 57
+Kajol Kanchan
 20% pred | 0% hist
 []</t>
         </is>
@@ -929,23 +964,58 @@
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Shruti Kulkarni
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
+          <t>Cardio Barre
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -953,37 +1023,51 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Recovery
 Shruti Kulkarni
-50% pred | 0% hist
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pushyank Nahar
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -995,30 +1079,23 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pushyank Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
 Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Siddhartha Kusuma
 20% pred | 0% hist
 []</t>
         </is>
@@ -1032,38 +1109,24 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Kajol Kanchan
-48% pred | 0% hist
+          <t>FIT
+Chaitanya Nahar
+45% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-41% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Chaitanya Nahar
-92% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
       <c r="H17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -1092,14 +1155,7 @@
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Siddhartha Kusuma
-56% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H18" s="7" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
@@ -1107,7 +1163,14 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Chaitanya Nahar
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Mat 57
@@ -1119,14 +1182,7 @@
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
@@ -1135,14 +1191,7 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B20" s="7" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -1160,19 +1209,12 @@
 []</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Siddhartha Kusuma
+Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
@@ -1184,7 +1226,14 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -1212,69 +1261,20 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Recovery
-Pushyank Nahar
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+51% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E22" s="7" t="n"/>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1290,7 +1290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1384,8 +1384,8 @@
       <c r="D3" s="6" t="inlineStr">
         <is>
           <t>FIT
-Pushyank Nahar
-67% pred | 0% hist
+Kajol Kanchan
+69% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1400,7 +1400,7 @@
       <c r="F3" s="6" t="inlineStr">
         <is>
           <t>FIT
-Siddhartha Kusuma
+Shruti Kulkarni
 46% pred | 0% hist
 []</t>
         </is>
@@ -1409,59 +1409,108 @@
       <c r="H3" s="7" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>08:30</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>07:45</t>
         </is>
       </c>
       <c r="B4" s="7" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-20% pred | 0% hist
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+32% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D4" s="7" t="n"/>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
-22% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>09:00</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>08:15</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
           <t>FIT
-Shruti Kulkarni
-71% pred | 0% hist
+Kajol Kanchan
+37% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F5" s="7" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+92% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
@@ -1469,80 +1518,87 @@
 []</t>
         </is>
       </c>
-      <c r="H5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="H7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
 85% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-69% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+62% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Siddhartha Kusuma
-23% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+57% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Siddhartha Kusuma
@@ -1550,142 +1606,121 @@
 []</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-84% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-0% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>Barre 57
+Kajol Kanchan
+69% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Shruti Kulkarni
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="n"/>
+          <t>Back Body Blaze
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-20% pred | 0% hist
+          <t>Barre 57
+Pushyank Nahar
+22% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H12" s="7" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C13" s="7" t="n"/>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Siddhartha Kusuma
+          <t>Barre 57
+Kajol Kanchan
 20% pred | 0% hist
 []</t>
         </is>
@@ -1698,23 +1733,58 @@
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Shruti Kulkarni
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
+          <t>Cardio Barre
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1722,37 +1792,51 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Recovery
 Shruti Kulkarni
-50% pred | 0% hist
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pushyank Nahar
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1764,30 +1848,23 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pushyank Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
 Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Siddhartha Kusuma
 20% pred | 0% hist
 []</t>
         </is>
@@ -1801,38 +1878,24 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Kajol Kanchan
-48% pred | 0% hist
+          <t>FIT
+Chaitanya Nahar
+45% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-41% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Chaitanya Nahar
-92% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
       <c r="H17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -1861,14 +1924,7 @@
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Siddhartha Kusuma
-56% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H18" s="7" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
@@ -1876,7 +1932,14 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Chaitanya Nahar
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Mat 57
@@ -1888,14 +1951,7 @@
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
@@ -1904,14 +1960,7 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B20" s="7" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -1929,19 +1978,12 @@
 []</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Siddhartha Kusuma
+Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
@@ -1953,7 +1995,14 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -1981,69 +2030,20 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Recovery
-Pushyank Nahar
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+51% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E22" s="7" t="n"/>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2059,7 +2059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2153,8 +2153,8 @@
       <c r="D3" s="6" t="inlineStr">
         <is>
           <t>FIT
-Pushyank Nahar
-67% pred | 0% hist
+Kajol Kanchan
+69% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2169,7 +2169,7 @@
       <c r="F3" s="6" t="inlineStr">
         <is>
           <t>FIT
-Siddhartha Kusuma
+Shruti Kulkarni
 46% pred | 0% hist
 []</t>
         </is>
@@ -2178,59 +2178,108 @@
       <c r="H3" s="7" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>08:30</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>07:45</t>
         </is>
       </c>
       <c r="B4" s="7" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-20% pred | 0% hist
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+32% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D4" s="7" t="n"/>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
-22% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>09:00</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>08:15</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
           <t>FIT
-Shruti Kulkarni
-71% pred | 0% hist
+Kajol Kanchan
+37% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F5" s="7" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+92% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+24% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
@@ -2238,80 +2287,87 @@
 []</t>
         </is>
       </c>
-      <c r="H5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="H7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
 85% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-69% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+62% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Siddhartha Kusuma
-23% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+57% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Siddhartha Kusuma
@@ -2319,142 +2375,121 @@
 []</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-84% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-0% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>Barre 57
+Kajol Kanchan
+69% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Shruti Kulkarni
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="n"/>
+          <t>Back Body Blaze
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-20% pred | 0% hist
+          <t>Barre 57
+Pushyank Nahar
+22% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H12" s="7" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C13" s="7" t="n"/>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Siddhartha Kusuma
+          <t>Barre 57
+Kajol Kanchan
 20% pred | 0% hist
 []</t>
         </is>
@@ -2467,23 +2502,58 @@
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Shruti Kulkarni
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
+          <t>Cardio Barre
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -2491,37 +2561,51 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Recovery
 Shruti Kulkarni
-50% pred | 0% hist
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pushyank Nahar
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2533,30 +2617,23 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pushyank Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
 Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Siddhartha Kusuma
 20% pred | 0% hist
 []</t>
         </is>
@@ -2570,38 +2647,24 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Kajol Kanchan
-48% pred | 0% hist
+          <t>FIT
+Chaitanya Nahar
+45% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-41% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Chaitanya Nahar
-92% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
       <c r="H17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -2630,14 +2693,7 @@
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Siddhartha Kusuma
-56% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H18" s="7" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
@@ -2645,7 +2701,14 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Chaitanya Nahar
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Mat 57
@@ -2657,14 +2720,7 @@
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
@@ -2673,14 +2729,7 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B20" s="7" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -2698,19 +2747,12 @@
 []</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Siddhartha Kusuma
+Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
@@ -2722,7 +2764,14 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -2750,69 +2799,20 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Recovery
-Pushyank Nahar
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+51% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E22" s="7" t="n"/>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kenkere.xlsx
+++ b/outputs/schedule_kenkere.xlsx
@@ -1008,14 +1008,7 @@
 []</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H14" s="7" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1055,14 +1048,7 @@
 []</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F15" s="7" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
@@ -1243,14 +1229,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n"/>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Recovery
-Pushyank Nahar
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="7" t="n"/>
@@ -1777,14 +1756,7 @@
 []</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H14" s="7" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1824,14 +1796,7 @@
 []</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F15" s="7" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
@@ -2012,14 +1977,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n"/>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Recovery
-Pushyank Nahar
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="7" t="n"/>
@@ -2546,14 +2504,7 @@
 []</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H14" s="7" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -2593,14 +2544,7 @@
 []</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F15" s="7" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
@@ -2781,14 +2725,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n"/>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Recovery
-Pushyank Nahar
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="7" t="n"/>

--- a/outputs/schedule_kenkere.xlsx
+++ b/outputs/schedule_kenkere.xlsx
@@ -47,13 +47,13 @@
       <sz val="9"/>
     </font>
     <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="0092400E"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="000C4A6E"/>
-      <sz val="9"/>
     </font>
     <font>
       <color rgb="00065F46"/>
@@ -89,12 +89,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFBEB"/>
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
+        <fgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
     <fill>
@@ -148,10 +148,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -598,27 +598,20 @@
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-13% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="n"/>
       <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Shruti Kulkarni
-26% pred | 0% hist
+Kajol Kanchan
+47% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Kajol Kanchan
-20% pred | 0% hist
+          <t>Barre 57
+Kajol Kanchan
+33% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -631,27 +624,20 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-19% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>FIT
 Pushyank Nahar
-68% pred | 0% hist
+69% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -668,12 +654,33 @@
       <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
@@ -681,24 +688,24 @@
 []</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
-22% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
@@ -706,53 +713,32 @@
 []</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-54% pred | 0% hist
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+58% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -761,176 +747,169 @@
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+69% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Siddhartha Kusuma
 46% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-23% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-23% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Pushyank Nahar
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Chaitanya Nahar
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Barre 57
+Pushyank Nahar
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Siddhartha Kusuma
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Kajol Kanchan
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Shruti Kulkarni
 49% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
@@ -939,10 +918,10 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
 20% pred | 0% hist
 []</t>
         </is>
@@ -958,7 +937,7 @@
       <c r="D14" s="6" t="inlineStr">
         <is>
           <t>FIT
-Kajol Kanchan
+Pushyank Nahar
 20% pred | 0% hist
 []</t>
         </is>
@@ -971,10 +950,10 @@
 []</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
 20% pred | 0% hist
 []</t>
         </is>
@@ -988,8 +967,7 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Pushyank Nahar
@@ -997,23 +975,24 @@
 []</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Shruti Kulkarni
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n"/>
       <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Recovery
@@ -1022,7 +1001,14 @@
 []</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -1031,10 +1017,10 @@
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Kajol Kanchan
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
@@ -1042,26 +1028,19 @@
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>FIT
+          <t>Cardio Barre
 Pushyank Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G16" s="5" t="n"/>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Siddhartha Kusuma
-20% pred | 0% hist
+          <t>Barre 57
+Chaitanya Nahar
+27% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1072,27 +1051,34 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Chaitanya Nahar
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -1113,31 +1099,38 @@
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Chaitanya Nahar
+58% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Chaitanya Nahar
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
@@ -1162,15 +1155,29 @@
       </c>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+12% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C21" s="5" t="n"/>
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="9" t="inlineStr">
@@ -1186,25 +1193,46 @@
       <c r="H21" s="5" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+77% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1220,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1297,27 +1325,20 @@
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-13% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="n"/>
       <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Shruti Kulkarni
-26% pred | 0% hist
+Kajol Kanchan
+47% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Kajol Kanchan
-20% pred | 0% hist
+          <t>Barre 57
+Kajol Kanchan
+33% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1330,27 +1351,20 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-19% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>FIT
 Pushyank Nahar
-68% pred | 0% hist
+69% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1367,12 +1381,33 @@
       <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
@@ -1380,24 +1415,24 @@
 []</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
-22% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
@@ -1405,53 +1440,32 @@
 []</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-54% pred | 0% hist
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+58% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1460,176 +1474,169 @@
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+69% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Siddhartha Kusuma
 46% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-23% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-23% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Pushyank Nahar
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Chaitanya Nahar
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Barre 57
+Pushyank Nahar
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Siddhartha Kusuma
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Kajol Kanchan
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Shruti Kulkarni
 49% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
@@ -1638,10 +1645,10 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
 20% pred | 0% hist
 []</t>
         </is>
@@ -1657,7 +1664,7 @@
       <c r="D14" s="6" t="inlineStr">
         <is>
           <t>FIT
-Kajol Kanchan
+Pushyank Nahar
 20% pred | 0% hist
 []</t>
         </is>
@@ -1670,10 +1677,10 @@
 []</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
 20% pred | 0% hist
 []</t>
         </is>
@@ -1687,8 +1694,7 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Pushyank Nahar
@@ -1696,23 +1702,24 @@
 []</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Shruti Kulkarni
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n"/>
       <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Recovery
@@ -1721,7 +1728,14 @@
 []</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -1730,10 +1744,10 @@
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Kajol Kanchan
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
@@ -1741,26 +1755,19 @@
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>FIT
+          <t>Cardio Barre
 Pushyank Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G16" s="5" t="n"/>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Siddhartha Kusuma
-20% pred | 0% hist
+          <t>Barre 57
+Chaitanya Nahar
+27% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1771,27 +1778,34 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Chaitanya Nahar
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -1812,31 +1826,38 @@
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Chaitanya Nahar
+58% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Chaitanya Nahar
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
@@ -1861,15 +1882,29 @@
       </c>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+12% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C21" s="5" t="n"/>
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="9" t="inlineStr">
@@ -1885,25 +1920,46 @@
       <c r="H21" s="5" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+77% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1919,7 +1975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1996,27 +2052,20 @@
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-13% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="n"/>
       <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Shruti Kulkarni
-26% pred | 0% hist
+Kajol Kanchan
+47% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Kajol Kanchan
-20% pred | 0% hist
+          <t>Barre 57
+Kajol Kanchan
+33% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2029,27 +2078,20 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-19% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+48% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>FIT
 Pushyank Nahar
-68% pred | 0% hist
+69% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2066,12 +2108,33 @@
       <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
@@ -2079,24 +2142,24 @@
 []</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
-22% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
@@ -2104,53 +2167,32 @@
 []</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-54% pred | 0% hist
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+58% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2159,176 +2201,169 @@
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+69% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Siddhartha Kusuma
 46% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-23% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-23% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Pushyank Nahar
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Chaitanya Nahar
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Barre 57
+Pushyank Nahar
+85% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Siddhartha Kusuma
+56% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Kajol Kanchan
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Shruti Kulkarni
 49% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
@@ -2337,10 +2372,10 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
 20% pred | 0% hist
 []</t>
         </is>
@@ -2356,7 +2391,7 @@
       <c r="D14" s="6" t="inlineStr">
         <is>
           <t>FIT
-Kajol Kanchan
+Pushyank Nahar
 20% pred | 0% hist
 []</t>
         </is>
@@ -2369,10 +2404,10 @@
 []</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
 20% pred | 0% hist
 []</t>
         </is>
@@ -2386,8 +2421,7 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Pushyank Nahar
@@ -2395,23 +2429,24 @@
 []</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Shruti Kulkarni
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n"/>
       <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Recovery
@@ -2420,7 +2455,14 @@
 []</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -2429,10 +2471,10 @@
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Kajol Kanchan
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Chaitanya Nahar
 20% pred | 0% hist
 []</t>
         </is>
@@ -2440,26 +2482,19 @@
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>FIT
+          <t>Cardio Barre
 Pushyank Nahar
 20% pred | 0% hist
 []</t>
         </is>
       </c>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G16" s="5" t="n"/>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Siddhartha Kusuma
-20% pred | 0% hist
+          <t>Barre 57
+Chaitanya Nahar
+27% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2470,27 +2505,34 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Chaitanya Nahar
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+41% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -2511,31 +2553,38 @@
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Chaitanya Nahar
+58% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Chaitanya Nahar
+35% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
@@ -2560,15 +2609,29 @@
       </c>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+12% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C21" s="5" t="n"/>
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="9" t="inlineStr">
@@ -2584,25 +2647,46 @@
       <c r="H21" s="5" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+77% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
